--- a/other/input/AQWMS/sgs_site_names_matching_table.xlsx
+++ b/other/input/AQWMS/sgs_site_names_matching_table.xlsx
@@ -18,24 +18,24 @@
     <t xml:space="preserve">V1</t>
   </si>
   <si>
+    <t xml:space="preserve">1212207001_MSD_FOR_[WXX13700]</t>
+  </si>
+  <si>
     <t xml:space="preserve">1212207001_MS_FOR_[WXX13700]</t>
   </si>
   <si>
-    <t xml:space="preserve">1212207001_MSD_FOR_[WXX13700]</t>
+    <t xml:space="preserve">1212275001_MSD_FOR_[WFI2930]</t>
   </si>
   <si>
     <t xml:space="preserve">1212275001_MS_FOR_[WFI2930]</t>
   </si>
   <si>
-    <t xml:space="preserve">1212275001_MSD_FOR_[WFI2930]</t>
+    <t xml:space="preserve">1212334001_MSD_FOR_[WFI2930]</t>
   </si>
   <si>
     <t xml:space="preserve">1212334001_MS_FOR_[WFI2930]</t>
   </si>
   <si>
-    <t xml:space="preserve">1212334001_MSD_FOR_[WFI2930]</t>
-  </si>
-  <si>
     <t xml:space="preserve">1212341014MS</t>
   </si>
   <si>
@@ -54,18 +54,18 @@
     <t xml:space="preserve">1212341040MS</t>
   </si>
   <si>
+    <t xml:space="preserve">1214541001_MSD_FOR_[WFI2945]</t>
+  </si>
+  <si>
     <t xml:space="preserve">1214541001_MS_FOR_[WFI2945]</t>
   </si>
   <si>
-    <t xml:space="preserve">1214541001_MSD_FOR_[WFI2945]</t>
+    <t xml:space="preserve">1214596001_MSD_FOR_[WFI2945]</t>
   </si>
   <si>
     <t xml:space="preserve">1214596001_MS_FOR_[WFI2945]</t>
   </si>
   <si>
-    <t xml:space="preserve">1214596001_MSD_FOR_[WFI2945]</t>
-  </si>
-  <si>
     <t xml:space="preserve">1214655001MS</t>
   </si>
   <si>
@@ -186,66 +186,66 @@
     <t xml:space="preserve">ICV_for_HBN_1823635_(MMS/11231</t>
   </si>
   <si>
+    <t xml:space="preserve">LABREFQC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LCSD_for_HBN_1819576_[WXX/1370</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LCSD_for_HBN_1823418_[WXX/1383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LCSD_for_HBN_1823419_[WXX/1383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LCSD_for_HBN_1823630_[VXX/3759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LCS_for_HBN_1819376_[MXX/34173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LCS_for_HBN_1819377_[MXX/34174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LCS_for_HBN_1819451_(WFI/2930)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LCS_for_HBN_1819576_[WXX/13700</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LCS_for_HBN_1823321_[MXX/34483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LCS_for_HBN_1823365_(WFI/2945)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LCS_for_HBN_1823418_[WXX/13837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LCS_for_HBN_1823419_[WXX/13838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LCS_for_HBN_1823630_[VXX/37591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LLQC_for_HBN_1819376_[MXX/3417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LLQC_for_HBN_1819377_[MXX/3417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LLQC_for_HBN_1819451_[WFI/2930</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LLQC_for_HBN_1823321_[MXX/3448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LLQC_for_HBN_1823365_[WFI/2945</t>
+  </si>
+  <si>
     <t xml:space="preserve">Lab_Control_Sample</t>
   </si>
   <si>
-    <t xml:space="preserve">LABREFQC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LCS_for_HBN_1819376_[MXX/34173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LCS_for_HBN_1819377_[MXX/34174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LCS_for_HBN_1819451_(WFI/2930)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LCS_for_HBN_1819576_[WXX/13700</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LCS_for_HBN_1823321_[MXX/34483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LCS_for_HBN_1823365_(WFI/2945)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LCS_for_HBN_1823418_[WXX/13837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LCS_for_HBN_1823419_[WXX/13838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LCS_for_HBN_1823630_[VXX/37591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LCSD_for_HBN_1819576_[WXX/1370</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LCSD_for_HBN_1823418_[WXX/1383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LCSD_for_HBN_1823419_[WXX/1383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LCSD_for_HBN_1823630_[VXX/3759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LLQC_for_HBN_1819376_[MXX/3417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LLQC_for_HBN_1819377_[MXX/3417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LLQC_for_HBN_1819451_[WFI/2930</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LLQC_for_HBN_1823321_[MXX/3448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LLQC_for_HBN_1823365_[WFI/2945</t>
-  </si>
-  <si>
     <t xml:space="preserve">MB_for_HBN_1819376_[MXX/34173]</t>
   </si>
   <si>
@@ -297,169 +297,169 @@
     <t xml:space="preserve">QCS_for_HBN_1823635_(MMS/11231</t>
   </si>
   <si>
+    <t xml:space="preserve">RM0_No_Name_Creek</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RM1.5_Kenai_City_Dock</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RM10.1_Kenai_River</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RM10_Beaver_Creek</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RM10_Beaver_creek</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RM12.5_Pillar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RM12.5_Pillars</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RM18_Poachers_Cove</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RM19_Slikok_Creek</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RM21_Soldotna_Bridge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RM21_Solotna_Bridge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RM22_Soldotna_Creek</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RM23_Swiftwater</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RM23_Swiftwater_Park</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RM30_Funny_River</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RM31_Morgans_Landing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RM36_Moose_River</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RM40_Bings_Landing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RM43_Upstream_of_Dow_Island</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RM44_Mouth_of_Killey_River</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RM50_Skilak_Lake_Outflow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RM50_Skilak_Lake_Outlet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RM6.5_Cunning_Hem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RM6.5_Cunningham_Park</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RM70_Jims_Landing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RM74_Russian_River</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RM79.5_Juneau_Creek</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RM82_Kenai_Lake_Bridge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RM_0_No_Name_Creek</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RM_0_No_Name_Creek_</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RM_1.5_Kenai_City_Dock</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RM_10.1_Kenai_River</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RM_10_Beaver_Creek</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RM_12.5_Pillars</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RM_18_Poachers_Cove</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RM_19_Slikok_Creek</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RM_21_Soldotna_Bridge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RM_22_Soldotna_Creek</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RM_23_Swiftwater_Park</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RM_30_Funny_River</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RM_31_Morgans_Landing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RM_36_Moose_River</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RM_40_Bings_Landing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RM_43_Upstream_of_Dow_Isalnd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RM_43_Upstream_of_Dow_Island</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RM_44_Mouth_of_Killey_River</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RM_50_Skilak_Lake_Outflow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RM_6.5_Cunningham_Park</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RM_70_Jims_Landing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RM_74_Russian_River</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RM_79.5_Juneau_Creek</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RM_82_Kenai_Lake_Bridge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rm10.1_Kenai_River</t>
+  </si>
+  <si>
     <t xml:space="preserve">Rm_0_No_Name_Creek</t>
   </si>
   <si>
-    <t xml:space="preserve">RM_0_No_Name_Creek</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RM_0_No_Name_Creek_</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RM_1.5_Kenai_City_Dock</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RM_10.1_Kenai_River</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RM_10_Beaver_Creek</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RM_12.5_Pillars</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RM_18_Poachers_Cove</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RM_19_Slikok_Creek</t>
-  </si>
-  <si>
     <t xml:space="preserve">Rm_21_Soldotna_Bridge</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RM_21_Soldotna_Bridge</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RM_22_Soldotna_Creek</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RM_23_Swiftwater_Park</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RM_30_Funny_River</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RM_31_Morgans_Landing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RM_36_Moose_River</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RM_40_Bings_Landing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RM_43_Upstream_of_Dow_Isalnd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RM_43_Upstream_of_Dow_Island</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RM_44_Mouth_of_Killey_River</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RM_50_Skilak_Lake_Outflow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RM_6.5_Cunningham_Park</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RM_70_Jims_Landing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RM_74_Russian_River</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RM_79.5_Juneau_Creek</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RM_82_Kenai_Lake_Bridge</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RM0_No_Name_Creek</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RM1.5_Kenai_City_Dock</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rm10.1_Kenai_River</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RM10.1_Kenai_River</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RM10_Beaver_creek</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RM10_Beaver_Creek</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RM12.5_Pillar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RM12.5_Pillars</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RM18_Poachers_Cove</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RM19_Slikok_Creek</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RM21_Soldotna_Bridge</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RM21_Solotna_Bridge</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RM22_Soldotna_Creek</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RM23_Swiftwater</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RM23_Swiftwater_Park</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RM30_Funny_River</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RM31_Morgans_Landing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RM36_Moose_River</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RM40_Bings_Landing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RM43_Upstream_of_Dow_Island</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RM44_Mouth_of_Killey_River</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RM50_Skilak_Lake_Outflow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RM50_Skilak_Lake_Outlet</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RM6.5_Cunning_Hem</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RM6.5_Cunningham_Park</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RM70_Jims_Landing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RM74_Russian_River</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RM79.5_Juneau_Creek</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RM82_Kenai_Lake_Bridge</t>
   </si>
   <si>
     <t xml:space="preserve">Trip_Blank_1</t>
